--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线3层（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="445">
   <si>
     <t>ID</t>
   </si>
@@ -84,6 +84,9 @@
     <t/>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
@@ -96,7 +99,15 @@
     <t>正当你打算走上前去进行进一步调查时，大卫的大手从身后猛地拽住了你的肩膀。</t>
   </si>
   <si>
+    <t>20 leberch-suspense</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -259,6 +270,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -297,6 +313,9 @@
     <t>前脚步入屋内，方才微弱的福尔马林气息以5倍的浓度猛地冲进鼻腔，与其说是这个房间里的药物浓度更高，不如说此处才是刚才空气中那股刺鼻气味的真正来源。</t>
   </si>
   <si>
+    <t>16 enhanced_suspence</t>
+  </si>
+  <si>
     <t>18</t>
   </si>
   <si>
@@ -877,6 +896,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -907,6 +931,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadein(L,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -2737,21 +2766,21 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" ht="90" spans="1:12">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -2769,13 +2798,13 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -2784,12 +2813,12 @@
         <v>15</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="55.5" spans="1:12">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2807,7 +2836,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2822,12 +2851,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2845,7 +2874,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2860,12 +2889,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="30" spans="1:12">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2895,15 +2924,15 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2936,15 +2965,15 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="30" spans="1:12">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -2959,7 +2988,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2974,12 +3003,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:12">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2997,7 +3026,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3012,21 +3041,21 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:12">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -3035,7 +3064,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3047,15 +3076,15 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="54" spans="1:12">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3064,7 +3093,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -3073,7 +3102,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3085,15 +3114,15 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3126,12 +3155,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="67.5" spans="1:12">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3149,7 +3178,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3164,12 +3193,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" ht="54" spans="1:12">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3187,7 +3216,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3202,12 +3231,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" ht="27" spans="1:12">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3225,7 +3254,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3240,12 +3269,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="54" spans="1:12">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3263,7 +3292,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3275,15 +3304,15 @@
         <v>15</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" ht="90" spans="1:12">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3301,7 +3330,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3316,12 +3345,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" ht="55.5" spans="1:12">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3339,13 +3368,13 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
@@ -3354,12 +3383,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" ht="54" spans="1:12">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3377,7 +3406,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3389,15 +3418,15 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3415,7 +3444,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3430,12 +3459,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" ht="55.5" spans="1:12">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3453,7 +3482,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3465,15 +3494,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3506,12 +3535,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" ht="90" spans="1:12">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3529,7 +3558,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3544,12 +3573,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" ht="40.5" spans="1:12">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3567,7 +3596,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3579,15 +3608,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="L24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" ht="40.5" spans="1:12">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3605,13 +3634,13 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
@@ -3620,12 +3649,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" ht="40.5" spans="1:12">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3643,7 +3672,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3658,12 +3687,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:12">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3681,7 +3710,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3696,15 +3725,15 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3719,7 +3748,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3734,12 +3763,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" ht="67.5" spans="1:12">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3757,7 +3786,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3772,15 +3801,15 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -3795,7 +3824,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3810,12 +3839,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" ht="54" spans="1:12">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3833,7 +3862,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3848,12 +3877,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3871,13 +3900,13 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
@@ -3886,15 +3915,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -3909,7 +3938,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3924,12 +3953,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" ht="54" spans="1:12">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3947,7 +3976,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3962,15 +3991,15 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" ht="28.5" spans="1:12">
       <c r="A35" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -3985,7 +4014,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4000,12 +4029,12 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4023,7 +4052,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4038,12 +4067,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" ht="54" spans="1:12">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4061,7 +4090,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4076,12 +4105,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" ht="27" spans="1:12">
       <c r="A38" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4099,7 +4128,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4114,15 +4143,15 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" ht="40.5" spans="1:12">
       <c r="A39" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -4137,7 +4166,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4152,12 +4181,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" ht="54" spans="1:12">
       <c r="A40" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4175,7 +4204,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4190,15 +4219,15 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4213,7 +4242,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4228,12 +4257,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" ht="54" spans="1:12">
       <c r="A42" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4251,7 +4280,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4266,21 +4295,21 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" ht="30" spans="1:12">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4289,7 +4318,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4301,15 +4330,15 @@
         <v>15</v>
       </c>
       <c r="K43" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L43" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" ht="54" spans="1:12">
       <c r="A44" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4318,7 +4347,7 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4327,7 +4356,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4339,24 +4368,24 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L44" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" ht="42" spans="1:12">
       <c r="A45" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4365,7 +4394,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4376,32 +4405,31 @@
       <c r="J45" t="s">
         <v>15</v>
       </c>
-      <c r="K45"/>
       <c r="L45" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" ht="30" spans="1:12">
       <c r="A46" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G46" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4413,33 +4441,33 @@
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="L46" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" ht="30" spans="1:12">
       <c r="A47" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G47" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4451,15 +4479,15 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L47" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4468,7 +4496,7 @@
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4477,7 +4505,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4489,15 +4517,15 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L48" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4515,7 +4543,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4530,15 +4558,15 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" ht="27" spans="1:12">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -4553,7 +4581,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4568,12 +4596,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4591,7 +4619,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4606,12 +4634,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4629,7 +4657,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4644,21 +4672,21 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" ht="42" spans="1:12">
       <c r="A53" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4667,7 +4695,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4679,33 +4707,33 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L53" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" ht="30" spans="1:12">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
       </c>
       <c r="F54" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G54" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4717,15 +4745,15 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="L54" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" ht="54" spans="1:12">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4734,7 +4762,7 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4743,7 +4771,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4755,21 +4783,21 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" ht="43.5" spans="1:12">
       <c r="A56" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B56" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4778,7 +4806,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4790,21 +4818,21 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" ht="30" spans="1:12">
       <c r="A57" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4813,7 +4841,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4825,15 +4853,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L57" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" ht="54" spans="1:12">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4851,7 +4879,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4866,12 +4894,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" ht="27" spans="1:12">
       <c r="A59" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4889,7 +4917,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4904,12 +4932,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60" ht="40.5" spans="1:12">
       <c r="A60" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4927,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4939,15 +4967,15 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="L60" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" ht="43.5" spans="1:12">
       <c r="A61" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4965,7 +4993,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4980,12 +5008,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" ht="40.5" spans="1:12">
       <c r="A62" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5003,7 +5031,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5018,21 +5046,21 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" ht="55.5" spans="1:12">
       <c r="A63" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B63" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5041,7 +5069,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5053,24 +5081,24 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L63" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="64" ht="40.5" spans="1:12">
       <c r="A64" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B64" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5079,7 +5107,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5094,21 +5122,21 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="65" ht="43.5" spans="1:12">
       <c r="A65" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B65" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5117,7 +5145,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5132,12 +5160,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66" ht="40.5" spans="1:12">
       <c r="A66" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5146,7 +5174,7 @@
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5155,7 +5183,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5170,21 +5198,21 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" ht="70.5" spans="1:12">
       <c r="A67" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B67" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
@@ -5193,7 +5221,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5208,21 +5236,21 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5231,7 +5259,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5243,15 +5271,15 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L68" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" ht="27" spans="1:12">
       <c r="A69" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5269,7 +5297,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5284,12 +5312,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" ht="43.5" spans="1:12">
       <c r="A70" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5307,7 +5335,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5322,12 +5350,12 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" ht="55.5" spans="1:12">
       <c r="A71" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5345,7 +5373,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5357,15 +5385,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L71" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5383,7 +5411,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5398,12 +5426,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" ht="27" spans="1:12">
       <c r="A73" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5421,7 +5449,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5436,21 +5464,21 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" ht="30" spans="1:12">
       <c r="A74" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B74" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -5459,7 +5487,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5471,15 +5499,15 @@
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L74" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5488,7 +5516,7 @@
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -5497,7 +5525,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5509,18 +5537,18 @@
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L75" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B76" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5535,7 +5563,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5550,12 +5578,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="77" ht="67.5" spans="1:12">
       <c r="A77" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5573,7 +5601,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5588,12 +5616,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78" ht="40.5" spans="1:12">
       <c r="A78" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5611,7 +5639,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5623,15 +5651,15 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="L78" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="79" ht="40.5" spans="1:12">
       <c r="A79" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5649,7 +5677,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5661,24 +5689,24 @@
         <v>15</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="L79" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="80" ht="105" spans="1:12">
       <c r="A80" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B80" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
@@ -5687,7 +5715,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5699,10 +5727,10 @@
         <v>15</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L80" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -5723,39 +5751,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5763,82 +5791,82 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B10" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B11" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B12" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B14" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B15" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -5860,616 +5888,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E5" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D6" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F6" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C7" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E7" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B8" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C9" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E9" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B10" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C10" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D10" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E10" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F10" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B11" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D11" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C12" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D12" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E12" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F12" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B13" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C13" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D13" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E13" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F13" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B14" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D14" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E14" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F14" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B15" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C15" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D15" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E15" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F15" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C16" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D16" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E16" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F16" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C17" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F17" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B18" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C18" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D18" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E18" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F18" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B19" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C19" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D19" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E19" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F19" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B20" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C20" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D20" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E20" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F20" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B21" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C21" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D21" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E21" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F21" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B22" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C22" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D22" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E22" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F22" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B23" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C23" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D23" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E23" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F23" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B24" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C24" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D24" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E24" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F24" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B25" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C25" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D25" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E25" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F25" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B26" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C26" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D26" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E26" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F26" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B27" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C27" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D27" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E27" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F27" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B28" t="s">
+        <v>427</v>
+      </c>
+      <c r="C28" t="s">
+        <v>428</v>
+      </c>
+      <c r="D28" t="s">
         <v>424</v>
       </c>
-      <c r="C28" t="s">
-        <v>425</v>
-      </c>
-      <c r="D28" t="s">
-        <v>421</v>
-      </c>
       <c r="E28" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F28" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B29" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C29" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D29" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E29" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F29" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B30" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C30" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D30" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E30" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F30" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B31" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C31" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D31" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david3F(2).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_大卫线3层（中）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="447">
   <si>
     <t>ID</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>20 leberch-suspense</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music20)</t>
   </si>
   <si>
     <r>
@@ -322,7 +325,7 @@
     <t>你把手中的光圈往四面一扫，无数核桃状的大脑瞬间犹如漫天的炮弹般轰入你们的眼帘，它们或是被泡在标注着编号的透明标本瓶里，或是被打上蜡封陈列在两侧的铁架上。</t>
   </si>
   <si>
-    <t>bgfade(sntzm_david3F(2)_18,1)</t>
+    <t>bgfade(sntzm_david3F(2)_18,1)&amp;unlock(scene1)</t>
   </si>
   <si>
     <t>19</t>
@@ -455,6 +458,9 @@
   </si>
   <si>
     <t>她像条脱水的鱼儿，大口地呼吸着屋内掺着福尔马林的，算不上新鲜的空气。虽然身体仍有些脱力，但在看到来的人是你们后，她的眼神明显卸去了一丝疲惫的紧绷。</t>
+  </si>
+  <si>
+    <t>unlockscene(scene3)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=18</t>
@@ -2810,15 +2816,15 @@
         <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="55.5" spans="1:12">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2836,7 +2842,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2851,12 +2857,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2874,7 +2880,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2889,12 +2895,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="30" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2924,15 +2930,15 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2965,15 +2971,15 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="30" spans="1:12">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -2988,7 +2994,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3003,12 +3009,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:12">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -3026,7 +3032,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3041,21 +3047,21 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:12">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -3064,7 +3070,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3076,15 +3082,15 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="54" spans="1:12">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -3093,7 +3099,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -3102,7 +3108,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3114,15 +3120,15 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3155,12 +3161,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" ht="67.5" spans="1:12">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -3178,7 +3184,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3193,12 +3199,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="54" spans="1:12">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3216,7 +3222,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3231,12 +3237,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" ht="27" spans="1:12">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3254,7 +3260,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3269,12 +3275,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="54" spans="1:12">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -3292,7 +3298,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3304,15 +3310,15 @@
         <v>15</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" ht="90" spans="1:12">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3330,7 +3336,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3345,12 +3351,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" ht="55.5" spans="1:12">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3368,13 +3374,13 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
@@ -3383,12 +3389,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" ht="54" spans="1:12">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3406,7 +3412,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3418,15 +3424,15 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="40.5" spans="1:12">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3444,7 +3450,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3459,12 +3465,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" ht="55.5" spans="1:12">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3482,7 +3488,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3494,15 +3500,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3535,12 +3541,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" ht="90" spans="1:12">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3558,7 +3564,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3573,12 +3579,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" ht="40.5" spans="1:12">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3596,7 +3602,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3608,15 +3614,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" ht="40.5" spans="1:12">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3634,7 +3640,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3649,12 +3655,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" ht="40.5" spans="1:12">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3672,7 +3678,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3687,12 +3693,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:12">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3710,7 +3716,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3725,15 +3731,15 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3748,7 +3754,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3763,12 +3769,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" ht="67.5" spans="1:12">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3786,7 +3792,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3801,15 +3807,15 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -3824,7 +3830,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3839,12 +3845,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" ht="54" spans="1:12">
       <c r="A31" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3862,7 +3868,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3877,12 +3883,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3900,7 +3906,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3915,15 +3921,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -3938,7 +3944,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3953,12 +3959,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" ht="54" spans="1:12">
       <c r="A34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3976,7 +3982,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3988,18 +3994,18 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="L34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" ht="28.5" spans="1:12">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -4014,7 +4020,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4029,12 +4035,12 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4052,7 +4058,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4067,12 +4073,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" ht="54" spans="1:12">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4090,7 +4096,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4105,12 +4111,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" ht="27" spans="1:12">
       <c r="A38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4128,7 +4134,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4143,15 +4149,15 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" ht="40.5" spans="1:12">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -4166,7 +4172,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4181,12 +4187,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" ht="54" spans="1:12">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4204,7 +4210,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4219,15 +4225,15 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
@@ -4242,7 +4248,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4257,12 +4263,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" ht="54" spans="1:12">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4280,7 +4286,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4295,21 +4301,21 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" ht="30" spans="1:12">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4318,7 +4324,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4330,15 +4336,15 @@
         <v>15</v>
       </c>
       <c r="K43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L43" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" ht="54" spans="1:12">
       <c r="A44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4347,7 +4353,7 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4356,7 +4362,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4368,24 +4374,24 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L44" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" ht="42" spans="1:12">
       <c r="A45" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4394,7 +4400,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4406,30 +4412,30 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" ht="30" spans="1:12">
       <c r="A46" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G46" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4441,33 +4447,33 @@
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L46" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" ht="30" spans="1:12">
       <c r="A47" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4479,15 +4485,15 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L47" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4496,7 +4502,7 @@
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4505,7 +4511,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4517,15 +4523,15 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L48" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4543,7 +4549,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4558,15 +4564,15 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" ht="27" spans="1:12">
       <c r="A50" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -4581,7 +4587,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4596,12 +4602,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4619,7 +4625,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4634,12 +4640,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4657,7 +4663,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4672,21 +4678,21 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" ht="42" spans="1:12">
       <c r="A53" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
@@ -4695,7 +4701,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4707,33 +4713,33 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L53" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" ht="30" spans="1:12">
       <c r="A54" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
       </c>
       <c r="F54" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G54" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4745,15 +4751,15 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L54" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" ht="54" spans="1:12">
       <c r="A55" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4762,7 +4768,7 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E55" t="s">
         <v>15</v>
@@ -4771,7 +4777,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4783,21 +4789,21 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" ht="43.5" spans="1:12">
       <c r="A56" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B56" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4806,7 +4812,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4818,21 +4824,21 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" ht="30" spans="1:12">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4841,7 +4847,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4853,15 +4859,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" ht="54" spans="1:12">
       <c r="A58" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4879,7 +4885,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4894,12 +4900,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" ht="27" spans="1:12">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4917,7 +4923,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4932,12 +4938,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" ht="40.5" spans="1:12">
       <c r="A60" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4955,7 +4961,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4967,15 +4973,15 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L60" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" ht="43.5" spans="1:12">
       <c r="A61" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4993,7 +4999,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5008,12 +5014,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" ht="40.5" spans="1:12">
       <c r="A62" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5031,7 +5037,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5046,21 +5052,21 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="63" ht="55.5" spans="1:12">
       <c r="A63" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B63" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5069,7 +5075,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5081,24 +5087,24 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L63" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" ht="40.5" spans="1:12">
       <c r="A64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B64" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5107,7 +5113,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5122,21 +5128,21 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="65" ht="43.5" spans="1:12">
       <c r="A65" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B65" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -5145,7 +5151,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5160,12 +5166,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" ht="40.5" spans="1:12">
       <c r="A66" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5174,7 +5180,7 @@
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -5183,7 +5189,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5198,21 +5204,21 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" ht="70.5" spans="1:12">
       <c r="A67" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B67" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E67" t="s">
         <v>15</v>
@@ -5221,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5236,21 +5242,21 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5259,7 +5265,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5271,15 +5277,15 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L68" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" ht="27" spans="1:12">
       <c r="A69" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5297,7 +5303,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5312,12 +5318,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70" ht="43.5" spans="1:12">
       <c r="A70" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5335,7 +5341,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5350,12 +5356,12 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" ht="55.5" spans="1:12">
       <c r="A71" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5373,7 +5379,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5385,15 +5391,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L71" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5411,7 +5417,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5426,12 +5432,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="73" ht="27" spans="1:12">
       <c r="A73" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5449,7 +5455,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5464,21 +5470,21 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" ht="30" spans="1:12">
       <c r="A74" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B74" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -5487,7 +5493,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5499,15 +5505,15 @@
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L74" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="75" ht="40.5" spans="1:12">
       <c r="A75" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5516,7 +5522,7 @@
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -5525,7 +5531,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5537,18 +5543,18 @@
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L75" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5563,7 +5569,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5578,12 +5584,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="77" ht="67.5" spans="1:12">
       <c r="A77" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5601,7 +5607,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5616,12 +5622,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78" ht="40.5" spans="1:12">
       <c r="A78" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5639,7 +5645,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5651,15 +5657,15 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L78" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="79" ht="40.5" spans="1:12">
       <c r="A79" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5677,7 +5683,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5689,24 +5695,24 @@
         <v>15</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L79" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" ht="105" spans="1:12">
       <c r="A80" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B80" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
@@ -5715,7 +5721,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5727,10 +5733,10 @@
         <v>15</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L80" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -5751,39 +5757,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5791,15 +5797,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
@@ -5807,66 +5813,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -5888,616 +5894,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D13" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E13" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B14" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B16" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C16" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D16" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E16" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B17" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C17" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D17" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E17" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F17" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C18" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D18" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E18" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F18" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B19" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C19" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D19" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E19" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F19" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B20" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C20" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D20" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E20" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F20" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B21" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C21" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D21" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E21" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F21" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B22" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C22" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D22" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E22" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F22" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B23" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C23" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D23" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E23" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F23" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C24" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D24" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E24" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F24" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B25" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C25" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D25" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E25" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F25" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B26" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C26" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D26" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E26" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F26" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B27" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C27" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D27" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E27" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F27" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B28" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C28" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D28" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E28" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F28" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B29" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C29" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D29" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E29" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F29" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B30" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C30" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D30" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E30" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F30" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B31" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D31" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
